--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/4.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/4.xlsx
@@ -426,13 +426,13 @@
         <v>-14.98800995396466</v>
       </c>
       <c r="E2">
-        <v>-10.07928479859795</v>
+        <v>-8.156050944488369</v>
       </c>
       <c r="F2">
-        <v>-1.917554143002286</v>
+        <v>-2.667480070316665</v>
       </c>
       <c r="G2">
-        <v>-9.585013718883584</v>
+        <v>-10.35450368184962</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.00858322635584</v>
       </c>
       <c r="E3">
-        <v>-10.9085661297266</v>
+        <v>-9.154144729674945</v>
       </c>
       <c r="F3">
-        <v>-1.901162786777487</v>
+        <v>-2.528570848914598</v>
       </c>
       <c r="G3">
-        <v>-9.376773783372348</v>
+        <v>-9.828597038572079</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.03209684593759</v>
       </c>
       <c r="E4">
-        <v>-10.88546638381347</v>
+        <v>-10.23051771655811</v>
       </c>
       <c r="F4">
-        <v>-1.790493417406579</v>
+        <v>-2.637040450768962</v>
       </c>
       <c r="G4">
-        <v>-9.282794016603518</v>
+        <v>-9.216169287625684</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.02531145372529</v>
       </c>
       <c r="E5">
-        <v>-12.45054775713041</v>
+        <v>-11.68999960449019</v>
       </c>
       <c r="F5">
-        <v>-1.731699919001805</v>
+        <v>-1.91185755282445</v>
       </c>
       <c r="G5">
-        <v>-9.102362663622159</v>
+        <v>-9.279185521965712</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.97279647093027</v>
       </c>
       <c r="E6">
-        <v>-13.07826671017765</v>
+        <v>-12.13566937395507</v>
       </c>
       <c r="F6">
-        <v>-1.675095102172168</v>
+        <v>-2.400440329973012</v>
       </c>
       <c r="G6">
-        <v>-8.641931990020323</v>
+        <v>-9.013504310802581</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.85504424722419</v>
       </c>
       <c r="E7">
-        <v>-13.76617361126083</v>
+        <v>-11.33884814451341</v>
       </c>
       <c r="F7">
-        <v>-1.566002312040079</v>
+        <v>-1.963452315990594</v>
       </c>
       <c r="G7">
-        <v>-8.711400477616388</v>
+        <v>-10.03700912245136</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.66561571195424</v>
       </c>
       <c r="E8">
-        <v>-14.41851387748777</v>
+        <v>-12.13488594795174</v>
       </c>
       <c r="F8">
-        <v>-1.431371472168572</v>
+        <v>-2.359560129177773</v>
       </c>
       <c r="G8">
-        <v>-8.379412349847195</v>
+        <v>-9.416675788757184</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.40928900547067</v>
       </c>
       <c r="E9">
-        <v>-14.6457119469266</v>
+        <v>-12.79306794564858</v>
       </c>
       <c r="F9">
-        <v>-1.395837070690899</v>
+        <v>-1.867459149338063</v>
       </c>
       <c r="G9">
-        <v>-8.122106818898422</v>
+        <v>-8.623204233904666</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.10357977103237</v>
       </c>
       <c r="E10">
-        <v>-15.9279720045685</v>
+        <v>-12.85513973887171</v>
       </c>
       <c r="F10">
-        <v>-1.087569506103568</v>
+        <v>-2.283328444938096</v>
       </c>
       <c r="G10">
-        <v>-7.835734698114845</v>
+        <v>-7.771592878291466</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.78087743465568</v>
       </c>
       <c r="E11">
-        <v>-16.40499239958848</v>
+        <v>-14.35409633472866</v>
       </c>
       <c r="F11">
-        <v>-1.369074024425888</v>
+        <v>-1.817459969881724</v>
       </c>
       <c r="G11">
-        <v>-6.62680623081149</v>
+        <v>-7.734720022075064</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.47882684275443</v>
       </c>
       <c r="E12">
-        <v>-17.09654019377382</v>
+        <v>-15.31711256025182</v>
       </c>
       <c r="F12">
-        <v>-0.9715400840618551</v>
+        <v>-1.785517413420268</v>
       </c>
       <c r="G12">
-        <v>-7.067592127183292</v>
+        <v>-7.218655630685775</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.22956603405588</v>
       </c>
       <c r="E13">
-        <v>-17.19097246225578</v>
+        <v>-14.95050994696087</v>
       </c>
       <c r="F13">
-        <v>-0.9397875723102519</v>
+        <v>-1.749633012935283</v>
       </c>
       <c r="G13">
-        <v>-5.832202469384542</v>
+        <v>-7.731204222712358</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.06126638049543</v>
       </c>
       <c r="E14">
-        <v>-17.8816824887497</v>
+        <v>-17.90000016611073</v>
       </c>
       <c r="F14">
-        <v>-0.8336175114451068</v>
+        <v>-1.572175597698462</v>
       </c>
       <c r="G14">
-        <v>-5.976631639626325</v>
+        <v>-6.539897789314542</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.98067908433905</v>
       </c>
       <c r="E15">
-        <v>-19.30831482623014</v>
+        <v>-16.88472535053905</v>
       </c>
       <c r="F15">
-        <v>-0.680112064473392</v>
+        <v>-1.272162308342402</v>
       </c>
       <c r="G15">
-        <v>-6.083549018362628</v>
+        <v>-5.276229451519338</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.97545419901879</v>
       </c>
       <c r="E16">
-        <v>-19.43926470910995</v>
+        <v>-17.12208078717709</v>
       </c>
       <c r="F16">
-        <v>-0.270387547825264</v>
+        <v>-1.06431991141196</v>
       </c>
       <c r="G16">
-        <v>-5.475580572257631</v>
+        <v>-5.316121525267556</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.01565920166517</v>
       </c>
       <c r="E17">
-        <v>-21.17870591714422</v>
+        <v>-18.77798976366588</v>
       </c>
       <c r="F17">
-        <v>-0.2905623774820471</v>
+        <v>-1.394441825779397</v>
       </c>
       <c r="G17">
-        <v>-4.904385666002859</v>
+        <v>-5.101032071035568</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.05994948824106</v>
       </c>
       <c r="E18">
-        <v>-21.54716520477832</v>
+        <v>-20.40350362261518</v>
       </c>
       <c r="F18">
-        <v>-0.1644930517894053</v>
+        <v>-1.135651609549268</v>
       </c>
       <c r="G18">
-        <v>-4.550170535482999</v>
+        <v>-5.549498433058478</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.06656419809844</v>
       </c>
       <c r="E19">
-        <v>-23.03580140837178</v>
+        <v>-20.54190737371161</v>
       </c>
       <c r="F19">
-        <v>0.1574791119371807</v>
+        <v>-0.3294985792660836</v>
       </c>
       <c r="G19">
-        <v>-4.100363402516684</v>
+        <v>-4.260368689520739</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.00366408813655</v>
       </c>
       <c r="E20">
-        <v>-23.27386781542902</v>
+        <v>-21.32565942716713</v>
       </c>
       <c r="F20">
-        <v>0.2192000907266445</v>
+        <v>-0.3042432210325707</v>
       </c>
       <c r="G20">
-        <v>-4.31082802463031</v>
+        <v>-3.782133902008701</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.84889927723224</v>
       </c>
       <c r="E21">
-        <v>-24.10438541996175</v>
+        <v>-21.97007939235466</v>
       </c>
       <c r="F21">
-        <v>0.4194929615581869</v>
+        <v>-0.1764207328915375</v>
       </c>
       <c r="G21">
-        <v>-3.510050095772621</v>
+        <v>-4.270131488316049</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.59866044290802</v>
       </c>
       <c r="E22">
-        <v>-25.00123158328484</v>
+        <v>-23.04790601939429</v>
       </c>
       <c r="F22">
-        <v>0.3631431213809359</v>
+        <v>-0.09778973418996893</v>
       </c>
       <c r="G22">
-        <v>-3.92985706506206</v>
+        <v>-3.629094002819273</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.26285078816476</v>
       </c>
       <c r="E23">
-        <v>-24.93019794000052</v>
+        <v>-23.2351267202934</v>
       </c>
       <c r="F23">
-        <v>0.8921729557568638</v>
+        <v>0.03897831681442403</v>
       </c>
       <c r="G23">
-        <v>-3.526076446728232</v>
+        <v>-3.612971646043023</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.86207103955535</v>
       </c>
       <c r="E24">
-        <v>-25.15397701156356</v>
+        <v>-23.83515405478373</v>
       </c>
       <c r="F24">
-        <v>0.7581946027225175</v>
+        <v>-0.2477651006761692</v>
       </c>
       <c r="G24">
-        <v>-4.118746861896256</v>
+        <v>-3.64196540387596</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.42895887371077</v>
       </c>
       <c r="E25">
-        <v>-25.60991736007784</v>
+        <v>-24.95792578634949</v>
       </c>
       <c r="F25">
-        <v>0.5062151137817356</v>
+        <v>-0.1717385063525408</v>
       </c>
       <c r="G25">
-        <v>-3.668055813270956</v>
+        <v>-4.085505674136434</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.99595779383903</v>
       </c>
       <c r="E26">
-        <v>-25.78103027893167</v>
+        <v>-25.26157808245982</v>
       </c>
       <c r="F26">
-        <v>0.634382057959377</v>
+        <v>-0.3844017040895806</v>
       </c>
       <c r="G26">
-        <v>-4.11164574171452</v>
+        <v>-3.650394052818944</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.59037869392108</v>
       </c>
       <c r="E27">
-        <v>-26.31720612991385</v>
+        <v>-24.60723170224748</v>
       </c>
       <c r="F27">
-        <v>0.5503205316737665</v>
+        <v>-0.1566758793907962</v>
       </c>
       <c r="G27">
-        <v>-4.236347371087787</v>
+        <v>-3.967918407127061</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.23239147207199</v>
       </c>
       <c r="E28">
-        <v>-25.65726708430204</v>
+        <v>-24.53227640047252</v>
       </c>
       <c r="F28">
-        <v>0.4370269616009748</v>
+        <v>-0.4861191757734677</v>
       </c>
       <c r="G28">
-        <v>-3.997220045695151</v>
+        <v>-4.095076461290468</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.930945100158517</v>
       </c>
       <c r="E29">
-        <v>-26.25504376721056</v>
+        <v>-25.71626404367397</v>
       </c>
       <c r="F29">
-        <v>0.3964476649296698</v>
+        <v>-0.111605192743305</v>
       </c>
       <c r="G29">
-        <v>-3.965862558347174</v>
+        <v>-4.347280441563226</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.685959380417282</v>
       </c>
       <c r="E30">
-        <v>-26.15142775344105</v>
+        <v>-25.31456575682357</v>
       </c>
       <c r="F30">
-        <v>0.6510268071306455</v>
+        <v>-0.1515755544901234</v>
       </c>
       <c r="G30">
-        <v>-3.636145464817921</v>
+        <v>-3.677682879699157</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.496065924681782</v>
       </c>
       <c r="E31">
-        <v>-26.1759584971406</v>
+        <v>-25.5512102230424</v>
       </c>
       <c r="F31">
-        <v>0.3699696857294377</v>
+        <v>-0.1649491590930519</v>
       </c>
       <c r="G31">
-        <v>-3.213650332550593</v>
+        <v>-3.350190472772293</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.352879913142642</v>
       </c>
       <c r="E32">
-        <v>-26.33062399839857</v>
+        <v>-23.46273688086693</v>
       </c>
       <c r="F32">
-        <v>0.3915690588571586</v>
+        <v>-0.05051611261410142</v>
       </c>
       <c r="G32">
-        <v>-3.815222804673717</v>
+        <v>-3.546833567259463</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.247700598792376</v>
       </c>
       <c r="E33">
-        <v>-25.19627748726921</v>
+        <v>-24.06298158210963</v>
       </c>
       <c r="F33">
-        <v>0.5264334953511933</v>
+        <v>-0.4194435730275516</v>
       </c>
       <c r="G33">
-        <v>-2.919438839930023</v>
+        <v>-3.594710676848403</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.170693365597534</v>
       </c>
       <c r="E34">
-        <v>-26.19020054789472</v>
+        <v>-23.06011931379297</v>
       </c>
       <c r="F34">
-        <v>0.4616393352328192</v>
+        <v>-0.2499419044569407</v>
       </c>
       <c r="G34">
-        <v>-3.01724890788779</v>
+        <v>-3.318018591221656</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.11189046185685</v>
       </c>
       <c r="E35">
-        <v>-24.05454503503334</v>
+        <v>-23.80757564807702</v>
       </c>
       <c r="F35">
-        <v>0.6841611022934696</v>
+        <v>-0.2842742731447948</v>
       </c>
       <c r="G35">
-        <v>-3.218291717396651</v>
+        <v>-3.204288109765534</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.0660332290069</v>
       </c>
       <c r="E36">
-        <v>-24.39257297733589</v>
+        <v>-24.60767549270023</v>
       </c>
       <c r="F36">
-        <v>0.3877737076308079</v>
+        <v>-0.1230110427462999</v>
       </c>
       <c r="G36">
-        <v>-2.739917886971964</v>
+        <v>-2.254485973457552</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.031234433411038</v>
       </c>
       <c r="E37">
-        <v>-24.43706523446125</v>
+        <v>-23.23050314833157</v>
       </c>
       <c r="F37">
-        <v>0.3788099321494207</v>
+        <v>-0.3811551069629298</v>
       </c>
       <c r="G37">
-        <v>-2.30781886209521</v>
+        <v>-1.865337966407302</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.005022738144383</v>
       </c>
       <c r="E38">
-        <v>-24.55375948116491</v>
+        <v>-22.03614077117855</v>
       </c>
       <c r="F38">
-        <v>0.5088464411602382</v>
+        <v>-0.2552156451553541</v>
       </c>
       <c r="G38">
-        <v>-2.603367815113645</v>
+        <v>-3.152133775339856</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.986294330801954</v>
       </c>
       <c r="E39">
-        <v>-23.56628496752632</v>
+        <v>-22.26568006167935</v>
       </c>
       <c r="F39">
-        <v>0.6512865349007776</v>
+        <v>-0.09067889462964582</v>
       </c>
       <c r="G39">
-        <v>-2.182610719254435</v>
+        <v>-3.059415326421487</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.969977525037203</v>
       </c>
       <c r="E40">
-        <v>-22.95875848007929</v>
+        <v>-21.33507865310309</v>
       </c>
       <c r="F40">
-        <v>0.3338944486816425</v>
+        <v>0.004950811515292061</v>
       </c>
       <c r="G40">
-        <v>-2.751782882184712</v>
+        <v>-2.687799968547218</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.946451863548411</v>
       </c>
       <c r="E41">
-        <v>-23.29232587548428</v>
+        <v>-22.67421634428133</v>
       </c>
       <c r="F41">
-        <v>0.5433870671759726</v>
+        <v>0.08558044708214521</v>
       </c>
       <c r="G41">
-        <v>-2.698499651730142</v>
+        <v>-2.863437651587712</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.908645302606661</v>
       </c>
       <c r="E42">
-        <v>-22.63131811000667</v>
+        <v>-21.53741992871381</v>
       </c>
       <c r="F42">
-        <v>0.6891117669851333</v>
+        <v>0.210321835364691</v>
       </c>
       <c r="G42">
-        <v>-3.101492360225624</v>
+        <v>-2.509656202533496</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.850989207275768</v>
       </c>
       <c r="E43">
-        <v>-22.52136223262642</v>
+        <v>-20.76054209880193</v>
       </c>
       <c r="F43">
-        <v>0.6633211161522019</v>
+        <v>0.2717910049136</v>
       </c>
       <c r="G43">
-        <v>-2.928893757990181</v>
+        <v>-3.252307572812662</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.773360517161718</v>
       </c>
       <c r="E44">
-        <v>-22.41746092499443</v>
+        <v>-20.81533663429475</v>
       </c>
       <c r="F44">
-        <v>0.608016521879141</v>
+        <v>-0.03595393672163571</v>
       </c>
       <c r="G44">
-        <v>-3.088697101716341</v>
+        <v>-3.357970254789581</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.678622574639743</v>
       </c>
       <c r="E45">
-        <v>-21.98331159340507</v>
+        <v>-20.0884259865835</v>
       </c>
       <c r="F45">
-        <v>0.5965647444045984</v>
+        <v>0.1289280616936383</v>
       </c>
       <c r="G45">
-        <v>-2.941000423027296</v>
+        <v>-2.993790382196515</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.568037594681531</v>
       </c>
       <c r="E46">
-        <v>-21.2662458481865</v>
+        <v>-19.25777252783053</v>
       </c>
       <c r="F46">
-        <v>0.5428953264892287</v>
+        <v>0.2288100182215311</v>
       </c>
       <c r="G46">
-        <v>-3.742685441362746</v>
+        <v>-3.58858947814629</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.444010003988659</v>
       </c>
       <c r="E47">
-        <v>-20.53319458972085</v>
+        <v>-19.83905650840311</v>
       </c>
       <c r="F47">
-        <v>0.7603674472385004</v>
+        <v>-0.2396921597722166</v>
       </c>
       <c r="G47">
-        <v>-3.924503912925059</v>
+        <v>-4.027422152649922</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.314266559924583</v>
       </c>
       <c r="E48">
-        <v>-20.71895259351549</v>
+        <v>-18.92303678613155</v>
       </c>
       <c r="F48">
-        <v>0.7032748489869083</v>
+        <v>0.08803044013333003</v>
       </c>
       <c r="G48">
-        <v>-2.822396818537367</v>
+        <v>-4.231487490236137</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.187279121878159</v>
       </c>
       <c r="E49">
-        <v>-20.34088841251112</v>
+        <v>-18.54801121118633</v>
       </c>
       <c r="F49">
-        <v>1.111031611035103</v>
+        <v>0.0297872795341712</v>
       </c>
       <c r="G49">
-        <v>-3.252923334282967</v>
+        <v>-4.610415843206656</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.074045681807814</v>
       </c>
       <c r="E50">
-        <v>-19.64477591652604</v>
+        <v>-16.99014369696361</v>
       </c>
       <c r="F50">
-        <v>0.6827706084997138</v>
+        <v>0.385417153228634</v>
       </c>
       <c r="G50">
-        <v>-3.814401789379978</v>
+        <v>-5.005367236587248</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.980971333663088</v>
       </c>
       <c r="E51">
-        <v>-19.24154247698704</v>
+        <v>-17.55786942635723</v>
       </c>
       <c r="F51">
-        <v>0.8366656471266266</v>
+        <v>-0.263488133004652</v>
       </c>
       <c r="G51">
-        <v>-4.367348968622287</v>
+        <v>-3.442802984233405</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.9105764369655</v>
       </c>
       <c r="E52">
-        <v>-19.57140105217976</v>
+        <v>-18.0149283079514</v>
       </c>
       <c r="F52">
-        <v>0.5608711804824241</v>
+        <v>0.5029297158601564</v>
       </c>
       <c r="G52">
-        <v>-4.618155898677473</v>
+        <v>-4.538322092997948</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.865915607238608</v>
       </c>
       <c r="E53">
-        <v>-18.16794544467058</v>
+        <v>-16.99661941479458</v>
       </c>
       <c r="F53">
-        <v>0.4079026098160433</v>
+        <v>0.2399157559535502</v>
       </c>
       <c r="G53">
-        <v>-4.499416561820433</v>
+        <v>-4.532005572109018</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.848603674605601</v>
       </c>
       <c r="E54">
-        <v>-17.82882161165817</v>
+        <v>-17.02899800394942</v>
       </c>
       <c r="F54">
-        <v>0.7724051959017556</v>
+        <v>0.0927023725838764</v>
       </c>
       <c r="G54">
-        <v>-4.76179715908091</v>
+        <v>-4.321193342713769</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.858058193496277</v>
       </c>
       <c r="E55">
-        <v>-18.585008843829</v>
+        <v>-15.00286816343755</v>
       </c>
       <c r="F55">
-        <v>0.7618102033274657</v>
+        <v>-0.1382035335931105</v>
       </c>
       <c r="G55">
-        <v>-5.002367882328668</v>
+        <v>-3.857730209397959</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.894582635108025</v>
       </c>
       <c r="E56">
-        <v>-18.20673182454627</v>
+        <v>-16.11787809055416</v>
       </c>
       <c r="F56">
-        <v>0.387242374296178</v>
+        <v>0.107685814249849</v>
       </c>
       <c r="G56">
-        <v>-4.757364338603826</v>
+        <v>-4.659978020475085</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.957395167938214</v>
       </c>
       <c r="E57">
-        <v>-17.28076304487986</v>
+        <v>-16.12181786294083</v>
       </c>
       <c r="F57">
-        <v>0.8114261259522682</v>
+        <v>0.1647174398236967</v>
       </c>
       <c r="G57">
-        <v>-4.902690666686752</v>
+        <v>-4.75266336393806</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.045527717146564</v>
       </c>
       <c r="E58">
-        <v>-17.90670230764208</v>
+        <v>-16.1310695353385</v>
       </c>
       <c r="F58">
-        <v>0.4111119898536814</v>
+        <v>-0.0909473327823128</v>
       </c>
       <c r="G58">
-        <v>-5.07122391899997</v>
+        <v>-5.340606320076006</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.162042091614925</v>
       </c>
       <c r="E59">
-        <v>-16.46099603764134</v>
+        <v>-14.5711460939163</v>
       </c>
       <c r="F59">
-        <v>0.645431574131398</v>
+        <v>-0.1092280501642303</v>
       </c>
       <c r="G59">
-        <v>-5.146134943462598</v>
+        <v>-4.817900974334939</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.307647343391926</v>
       </c>
       <c r="E60">
-        <v>-16.35716718559347</v>
+        <v>-13.88939791748355</v>
       </c>
       <c r="F60">
-        <v>0.3928399828542987</v>
+        <v>-0.05622933170404924</v>
       </c>
       <c r="G60">
-        <v>-5.559496280587077</v>
+        <v>-5.802599571172379</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.483690403160118</v>
       </c>
       <c r="E61">
-        <v>-16.36810345032199</v>
+        <v>-14.14616692219246</v>
       </c>
       <c r="F61">
-        <v>0.6957633318299791</v>
+        <v>-0.3127073372976369</v>
       </c>
       <c r="G61">
-        <v>-5.878182636379479</v>
+        <v>-5.305014644983301</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.688069303701921</v>
       </c>
       <c r="E62">
-        <v>-16.1822548770472</v>
+        <v>-14.02842206951903</v>
       </c>
       <c r="F62">
-        <v>0.6909346124938042</v>
+        <v>-0.286084449006142</v>
       </c>
       <c r="G62">
-        <v>-6.122540623724164</v>
+        <v>-5.92491760775737</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.91514279795055</v>
       </c>
       <c r="E63">
-        <v>-15.58956819892331</v>
+        <v>-14.77167145144995</v>
       </c>
       <c r="F63">
-        <v>0.577808915248049</v>
+        <v>-0.4831299308580758</v>
       </c>
       <c r="G63">
-        <v>-5.977561902922861</v>
+        <v>-6.499310501003078</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.159512128402568</v>
       </c>
       <c r="E64">
-        <v>-15.72693040099797</v>
+        <v>-13.19141969020731</v>
       </c>
       <c r="F64">
-        <v>0.2592567644458545</v>
+        <v>-0.4307726132936477</v>
       </c>
       <c r="G64">
-        <v>-6.651681669993573</v>
+        <v>-6.023512275007945</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.416809634792363</v>
       </c>
       <c r="E65">
-        <v>-14.86801020748913</v>
+        <v>-12.91772324965772</v>
       </c>
       <c r="F65">
-        <v>0.4587237326424952</v>
+        <v>-0.4076330861631619</v>
       </c>
       <c r="G65">
-        <v>-6.021370352044036</v>
+        <v>-5.655806671415554</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.680028906553769</v>
       </c>
       <c r="E66">
-        <v>-15.84393711240816</v>
+        <v>-13.51880571859184</v>
       </c>
       <c r="F66">
-        <v>0.3503206464365805</v>
+        <v>-0.2639545343967489</v>
       </c>
       <c r="G66">
-        <v>-6.400457611200441</v>
+        <v>-5.955407732174058</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.945734874890718</v>
       </c>
       <c r="E67">
-        <v>-15.590568991679</v>
+        <v>-12.1242893187738</v>
       </c>
       <c r="F67">
-        <v>0.5748125436560375</v>
+        <v>-0.4639560033398504</v>
       </c>
       <c r="G67">
-        <v>-6.896936815179401</v>
+        <v>-6.768421437344894</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.20752295739341</v>
       </c>
       <c r="E68">
-        <v>-14.92278662908591</v>
+        <v>-13.00140944931947</v>
       </c>
       <c r="F68">
-        <v>0.3207560244071568</v>
+        <v>-0.8997388171206191</v>
       </c>
       <c r="G68">
-        <v>-7.068151609379428</v>
+        <v>-7.051638608229544</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.45766860149567</v>
       </c>
       <c r="E69">
-        <v>-15.50298377589665</v>
+        <v>-14.15198148281831</v>
       </c>
       <c r="F69">
-        <v>0.07634981715400639</v>
+        <v>-0.3440726329529151</v>
       </c>
       <c r="G69">
-        <v>-7.334117527458936</v>
+        <v>-7.063927353271318</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.69145944370156</v>
       </c>
       <c r="E70">
-        <v>-15.86735837997583</v>
+        <v>-13.52790795134725</v>
       </c>
       <c r="F70">
-        <v>0.2846047694754206</v>
+        <v>-0.7313362404553232</v>
       </c>
       <c r="G70">
-        <v>-7.033933810685522</v>
+        <v>-6.342076140615393</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.90297359885632</v>
       </c>
       <c r="E71">
-        <v>-14.82048387277863</v>
+        <v>-13.24994568828244</v>
       </c>
       <c r="F71">
-        <v>-0.1352459627960273</v>
+        <v>-0.5248201972290615</v>
       </c>
       <c r="G71">
-        <v>-7.028550863638666</v>
+        <v>-6.935335832889407</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.08744453039252</v>
       </c>
       <c r="E72">
-        <v>-16.71586308326703</v>
+        <v>-13.5729209829835</v>
       </c>
       <c r="F72">
-        <v>-0.009298582458874367</v>
+        <v>-0.620677165172865</v>
       </c>
       <c r="G72">
-        <v>-7.823227457067479</v>
+        <v>-7.817106258365367</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.24164296523568</v>
       </c>
       <c r="E73">
-        <v>-15.02749400509126</v>
+        <v>-13.86863033568437</v>
       </c>
       <c r="F73">
-        <v>-0.01895206186643552</v>
+        <v>-0.74459581823234</v>
       </c>
       <c r="G73">
-        <v>-7.868893122236186</v>
+        <v>-7.596809316000105</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.36303256934821</v>
       </c>
       <c r="E74">
-        <v>-15.99075023973683</v>
+        <v>-13.09822369512945</v>
       </c>
       <c r="F74">
-        <v>0.074732061561385</v>
+        <v>-0.8780760957562807</v>
       </c>
       <c r="G74">
-        <v>-7.947406020245541</v>
+        <v>-7.613166721509644</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.4514949781248</v>
       </c>
       <c r="E75">
-        <v>-15.33660764085484</v>
+        <v>-13.55981105073129</v>
       </c>
       <c r="F75">
-        <v>0.1960455183899621</v>
+        <v>-0.664914822508835</v>
       </c>
       <c r="G75">
-        <v>-8.501955503528858</v>
+        <v>-7.088322763350208</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.5111980775896</v>
       </c>
       <c r="E76">
-        <v>-15.91340390368582</v>
+        <v>-14.44375106313251</v>
       </c>
       <c r="F76">
-        <v>0.05352465564773536</v>
+        <v>-0.8552295542201511</v>
       </c>
       <c r="G76">
-        <v>-7.610905618906322</v>
+        <v>-8.001586408541254</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.54398023219228</v>
       </c>
       <c r="E77">
-        <v>-16.81393171637714</v>
+        <v>-14.69969135709803</v>
       </c>
       <c r="F77">
-        <v>-0.1402409712533233</v>
+        <v>-0.5105818891963032</v>
       </c>
       <c r="G77">
-        <v>-8.608161114974218</v>
+        <v>-7.563329768961456</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.55381665899649</v>
       </c>
       <c r="E78">
-        <v>-16.38276664915883</v>
+        <v>-15.45703787861483</v>
       </c>
       <c r="F78">
-        <v>-0.1851485361915243</v>
+        <v>-0.9708290001058227</v>
       </c>
       <c r="G78">
-        <v>-7.947031928599604</v>
+        <v>-7.990145163157533</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.54159574859612</v>
       </c>
       <c r="E79">
-        <v>-17.5242590922723</v>
+        <v>-16.02230011814827</v>
       </c>
       <c r="F79">
-        <v>-0.09595897015172093</v>
+        <v>-0.6312959133358864</v>
       </c>
       <c r="G79">
-        <v>-7.922510717790222</v>
+        <v>-7.514913040449614</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.5046051629026</v>
       </c>
       <c r="E80">
-        <v>-17.86828273416101</v>
+        <v>-15.08495581177459</v>
       </c>
       <c r="F80">
-        <v>0.08348124489123022</v>
+        <v>-0.7412415291034392</v>
       </c>
       <c r="G80">
-        <v>-8.812703171118088</v>
+        <v>-7.294440639170771</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.44154206718882</v>
       </c>
       <c r="E81">
-        <v>-18.41661300937977</v>
+        <v>-17.38052985574285</v>
       </c>
       <c r="F81">
-        <v>-0.3661922534738579</v>
+        <v>-1.101628855367882</v>
       </c>
       <c r="G81">
-        <v>-8.119100843548763</v>
+        <v>-7.825607739310215</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.3510785864016</v>
       </c>
       <c r="E82">
-        <v>-19.32840313692817</v>
+        <v>-18.24571745727831</v>
       </c>
       <c r="F82">
-        <v>-0.1988650131251453</v>
+        <v>-0.7732569360370054</v>
       </c>
       <c r="G82">
-        <v>-7.895652261830115</v>
+        <v>-7.658378841939471</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.231939446702</v>
       </c>
       <c r="E83">
-        <v>-20.20617989620495</v>
+        <v>-19.43004926450434</v>
       </c>
       <c r="F83">
-        <v>-0.2441099074233349</v>
+        <v>-0.8661618761544296</v>
       </c>
       <c r="G83">
-        <v>-8.015166266343345</v>
+        <v>-6.740218899895843</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.08698912864707</v>
       </c>
       <c r="E84">
-        <v>-20.69763706636138</v>
+        <v>-19.55574158906123</v>
       </c>
       <c r="F84">
-        <v>0.1137324034349968</v>
+        <v>-0.7172863934265021</v>
       </c>
       <c r="G84">
-        <v>-8.054190977160273</v>
+        <v>-7.097724712681738</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.91948840468279</v>
       </c>
       <c r="E85">
-        <v>-21.60480362194795</v>
+        <v>-20.38046727533816</v>
       </c>
       <c r="F85">
-        <v>-0.2878043536303093</v>
+        <v>-1.002301987763351</v>
       </c>
       <c r="G85">
-        <v>-8.205585535216684</v>
+        <v>-7.221962865679507</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.7316729363145</v>
       </c>
       <c r="E86">
-        <v>-22.16579098201815</v>
+        <v>-20.64622982942631</v>
       </c>
       <c r="F86">
-        <v>-0.0568905289237452</v>
+        <v>-0.8418044791749709</v>
       </c>
       <c r="G86">
-        <v>-7.74295996992231</v>
+        <v>-7.274941525944464</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.53021172276644</v>
       </c>
       <c r="E87">
-        <v>-24.48988535528672</v>
+        <v>-22.86820711382191</v>
       </c>
       <c r="F87">
-        <v>-0.3634152251511348</v>
+        <v>-1.190314802926576</v>
       </c>
       <c r="G87">
-        <v>-8.07904986361466</v>
+        <v>-7.141837731992527</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.31862369739735</v>
       </c>
       <c r="E88">
-        <v>-26.52829188883338</v>
+        <v>-23.48334596607583</v>
       </c>
       <c r="F88">
-        <v>0.0476649437606094</v>
+        <v>-0.6809245056080124</v>
       </c>
       <c r="G88">
-        <v>-7.778700619564281</v>
+        <v>-6.720660196849829</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.10002494856729</v>
       </c>
       <c r="E89">
-        <v>-27.36855929790464</v>
+        <v>-25.70120686759846</v>
       </c>
       <c r="F89">
-        <v>-0.08822019119592607</v>
+        <v>-0.7603030135016684</v>
       </c>
       <c r="G89">
-        <v>-7.533769907841303</v>
+        <v>-6.762240648823075</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.875891292976572</v>
       </c>
       <c r="E90">
-        <v>-28.51292279353897</v>
+        <v>-25.17556877563213</v>
       </c>
       <c r="F90">
-        <v>0.1549649787964206</v>
+        <v>-0.9080778206183655</v>
       </c>
       <c r="G90">
-        <v>-7.107212736197289</v>
+        <v>-7.56344563805533</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.645286602971396</v>
       </c>
       <c r="E91">
-        <v>-30.8847042623453</v>
+        <v>-29.13909753694958</v>
       </c>
       <c r="F91">
-        <v>0.223544196052695</v>
+        <v>-0.7097645821811225</v>
       </c>
       <c r="G91">
-        <v>-7.914174764122337</v>
+        <v>-6.70897728164174</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.409245062273014</v>
       </c>
       <c r="E92">
-        <v>-32.78555386943497</v>
+        <v>-30.42140514356856</v>
       </c>
       <c r="F92">
-        <v>0.07914980921250334</v>
+        <v>-0.6531581816455703</v>
       </c>
       <c r="G92">
-        <v>-7.497963047288546</v>
+        <v>-6.112724856200225</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.172944741506504</v>
       </c>
       <c r="E93">
-        <v>-35.3081154088007</v>
+        <v>-33.42830056347666</v>
       </c>
       <c r="F93">
-        <v>0.1995455084630833</v>
+        <v>-0.6015990518625237</v>
       </c>
       <c r="G93">
-        <v>-7.850489799583378</v>
+        <v>-7.20241740481565</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.941618173071731</v>
       </c>
       <c r="E94">
-        <v>-36.72368468428041</v>
+        <v>-34.68220784535654</v>
       </c>
       <c r="F94">
-        <v>0.2856397212911602</v>
+        <v>-0.4405432869389513</v>
       </c>
       <c r="G94">
-        <v>-7.122957690782063</v>
+        <v>-5.448943922848655</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.72537331029007</v>
       </c>
       <c r="E95">
-        <v>-38.75341239739137</v>
+        <v>-39.05511065696739</v>
       </c>
       <c r="F95">
-        <v>0.3573182510239497</v>
+        <v>-0.3860709301244538</v>
       </c>
       <c r="G95">
-        <v>-7.212335799251306</v>
+        <v>-6.352239515420956</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.531009259556454</v>
       </c>
       <c r="E96">
-        <v>-40.9564561319609</v>
+        <v>-39.61177558859727</v>
       </c>
       <c r="F96">
-        <v>1.003923996268018</v>
+        <v>0.02550652244473837</v>
       </c>
       <c r="G96">
-        <v>-7.148740219441907</v>
+        <v>-6.41935751568414</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.360668990758359</v>
       </c>
       <c r="E97">
-        <v>-44.0272890763833</v>
+        <v>-41.802542630132</v>
       </c>
       <c r="F97">
-        <v>0.8033698139604277</v>
+        <v>-0.1295081962643902</v>
       </c>
       <c r="G97">
-        <v>-7.539646126173509</v>
+        <v>-6.35480849875943</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.213540725763005</v>
       </c>
       <c r="E98">
-        <v>-46.08273625762082</v>
+        <v>-44.68618657297334</v>
       </c>
       <c r="F98">
-        <v>0.7198910914516991</v>
+        <v>0.0418076074323566</v>
       </c>
       <c r="G98">
-        <v>-7.084621573437302</v>
+        <v>-6.7596716654846</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.087110863308403</v>
       </c>
       <c r="E99">
-        <v>-48.18203718114863</v>
+        <v>-46.1181489243608</v>
       </c>
       <c r="F99">
-        <v>0.7201302310449303</v>
+        <v>0.1105048107793312</v>
       </c>
       <c r="G99">
-        <v>-7.219486577616133</v>
+        <v>-7.306865116579655</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.971804535001832</v>
       </c>
       <c r="E100">
-        <v>-51.30243200934797</v>
+        <v>-48.88074449274011</v>
       </c>
       <c r="F100">
-        <v>1.160224684180483</v>
+        <v>-0.1397452713017908</v>
       </c>
       <c r="G100">
-        <v>-7.963528377021793</v>
+        <v>-7.538765521060063</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.864817934956306</v>
       </c>
       <c r="E101">
-        <v>-52.28075108066156</v>
+        <v>-51.28404074428433</v>
       </c>
       <c r="F101">
-        <v>1.129304409887443</v>
+        <v>0.1429058501033069</v>
       </c>
       <c r="G101">
-        <v>-8.446096668644735</v>
+        <v>-6.736921596538728</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.751006297262314</v>
       </c>
       <c r="E102">
-        <v>-55.03170733872265</v>
+        <v>-54.1130407233936</v>
       </c>
       <c r="F102">
-        <v>1.121252849013349</v>
+        <v>0.4158076778929593</v>
       </c>
       <c r="G102">
-        <v>-8.316545090056437</v>
+        <v>-7.334157254005407</v>
       </c>
     </row>
   </sheetData>
